--- a/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/SVR/0.xlsx
+++ b/src/main/resources/python/MultifacetedModeling/Results/OnTrain/KnowledgeKernel/SVR/0.xlsx
@@ -442,56 +442,56 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.103515625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.298828125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.083984375</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.673828125</t>
+          <t>1.11328125</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.376953125</t>
+          <t>1.474609375</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0.91796875</t>
+          <t>1.46484375</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.044921875</t>
+          <t>1.220703125</t>
         </is>
       </c>
     </row>
@@ -505,91 +505,91 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>0.78125</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0.908203125</t>
+          <t>1.455078125</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.50390625</t>
+          <t>1.171875</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.005859375</t>
+          <t>0.64453125</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0.791015625</t>
+          <t>1.484375</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.34765625</t>
+          <t>0.830078125</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.15234375</t>
+          <t>1.328125</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.357421875</t>
+          <t>0.908203125</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.23046875</t>
+          <t>0.869140625</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.259765625</t>
+          <t>1.044921875</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.474609375</t>
+          <t>1.298828125</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.64453125</t>
+          <t>1.240234375</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.2109375</t>
+          <t>0.68359375</t>
         </is>
       </c>
     </row>
@@ -617,154 +617,154 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1.269472041766324</t>
+          <t>1.3219550660981119</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1.290536536185403</t>
+          <t>1.3656548615248587</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1.322870356482941</t>
+          <t>1.4223078714077095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1.2957922455609214</t>
+          <t>1.0009816808276915</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0.9449227263751858</t>
+          <t>1.1367666784178274</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.3938142237013542</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.3968518301572024</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.2294368853997772</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>0.9356057167734226</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1.290536536185403</t>
+          <t>0.8623684550898352</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.3800169021724278</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.3948000127337243</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>0.6611525863996652</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.4093386782192132</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>0.5460850520769602</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>1.1605550541322165</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>0.5985576092469094</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1.1546763461722556</t>
+          <t>0.9099624653354814</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1.3158954734956332</t>
+          <t>1.0927866751200943</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1.327224726414446</t>
+          <t>1.2306852954451548</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0.9449227263751858</t>
+          <t>1.192311684395519</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1.3446019231434327</t>
+          <t>0.7479778471750498</t>
         </is>
       </c>
     </row>
@@ -802,17 +802,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0.19485357291517597</t>
+          <t>0.07973976430613458</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.20180212107507614</t>
+          <t>0.1428565374739222</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3529628980796726</t>
+          <t>0.6969119860551836</t>
         </is>
       </c>
     </row>
